--- a/divisaoTarefasApresentacaoFinal.xlsx
+++ b/divisaoTarefasApresentacaoFinal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heito\OneDrive\Documentos\GitHub\SistemaDeEventos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954EBD66-1243-4C37-8F2D-02B0B8380820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2998DC1-3614-4DA6-A357-3C15CF11C3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E302C4F0-2473-47E5-B39D-594781641582}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>nº</t>
   </si>
@@ -53,16 +54,43 @@
     <t>Trazer a relação de usuários confirmados em determinado evento ordenando por data crescente</t>
   </si>
   <si>
-    <t>trazer a programação completa de um evento ordenando por ordem cronologica</t>
-  </si>
-  <si>
     <t>trazer a quantidade de usuarios ligadas a cada cidade</t>
   </si>
   <si>
     <t>Fazer uma pesquisa que traga o valor total arrecadado, quantidade de inscritos confirmados, quantidade de incrições feitas e não confirmadas, e o valor projetado das inscrições que não formam confirmadas  de um evento X. Para isso é necessario que valide se o pagamento foi confirmado</t>
   </si>
   <si>
-    <t xml:space="preserve">Pesquias trazendo eventos com  inscrições abertas,  eventos em andamento e eventos futuros </t>
+    <t>trazer a programação completa de um evento ordenando por ordem cronologica e suas imagens</t>
+  </si>
+  <si>
+    <t>Trazer a quantidade de vouchers usuados e vouches disponiveis para cada evento</t>
+  </si>
+  <si>
+    <t>Pesquisar todos os eventos e os dados do usuario que cadastrou o evento e se tem permição para criar evento</t>
+  </si>
+  <si>
+    <t>Trazer a relação de todos os usuarios envolvidos em uma programação, trazendo os dados dos usuarios e inforamção da programação e do evento</t>
+  </si>
+  <si>
+    <t>Trazer todos os telefones cadastrados para o usuario</t>
+  </si>
+  <si>
+    <t>dificuldade</t>
+  </si>
+  <si>
+    <t>Pesquias trazendo eventos com  inscrições abertas,  eventos em andamento e eventos futuros com base na data atual do sistema</t>
+  </si>
+  <si>
+    <t>Gustavo</t>
+  </si>
+  <si>
+    <t>Heitor</t>
+  </si>
+  <si>
+    <t>Manoela</t>
+  </si>
+  <si>
+    <t>Fernando</t>
   </si>
 </sst>
 </file>
@@ -100,7 +128,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -108,25 +136,229 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -147,7 +379,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -463,96 +695,171 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{352F123A-EB98-4230-9175-D00F05ED069B}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="B1:E13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="70.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="83.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:5" ht="18.600000000000001" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+    <row r="3" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B3" s="8">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="11">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="D3" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="8">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="11">
+        <v>1</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="8">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C5" s="11">
+        <v>1</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="8">
+        <v>4</v>
+      </c>
+      <c r="C6" s="11">
+        <v>1</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
+    <row r="7" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B7" s="8">
+        <v>5</v>
+      </c>
+      <c r="C7" s="11">
+        <v>3</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1" t="s">
+    <row r="8" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="8">
+        <v>6</v>
+      </c>
+      <c r="C8" s="11">
+        <v>2</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="8">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="C9" s="11">
+        <v>2</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+    <row r="10" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="8">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+      <c r="C10" s="11">
+        <v>2</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+    <row r="11" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B11" s="8">
+        <v>9</v>
+      </c>
+      <c r="C11" s="11">
+        <v>2</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-    </row>
+    <row r="12" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="9">
+        <v>10</v>
+      </c>
+      <c r="C12" s="12">
+        <v>1</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
